--- a/data/manufacturing/RAGFlow_커넥팅로드_가공_오류DB.xlsx
+++ b/data/manufacturing/RAGFlow_커넥팅로드_가공_오류DB.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="오류주의사항DB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="출처" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'오류주의사항DB'!$A$1:$AA$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5036,8 +5036,943 @@
         </is>
       </c>
     </row>
+    <row r="35" ht="120" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Ø680(+0.08/0)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 대단부 보어를 캡 분할 방향으로만 재서 타원을 놓침</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Ø680(+0.08/0) 대단부 보어를 캡 분할면과 평행한 방향으로만 재서 680.050(합격)으로 기록했다. 분할면에 직각 방향은 680.095로 상한을 넘었다 (볼트 체결로 보어가 세로로 늘어남).</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>측정 방향 부족</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>대단부 보어는 분할면 평행·직각 2방향 × 입구·중간·안쪽 3단면(6점)을 재고, 가장 큰 값과 작은 값을 모두 기록한다.</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, Ø680 세팅 링</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>캡 체결 상태 대단부 보어 정삭 후</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>측정 위치</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>베어링 메탈 끼움 불량, 유막 불균일</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>6점 재측정 후 재호닝 여부 결정</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 대단부, 내경, DIMENSION, Ø680(+0.08/0), 측정 방향 부족, 대단부, C1 측정 위치, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-034] 부품: 커넥팅로드. 부위: 대단부. 형상: 대단부(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø680(+0.08/0). 오류 유형: C1 측정 위치. 중요도: 상. 오류: [정삭] 대단부 보어를 캡 분할 방향으로만 재서 타원을 놓침. 상황: Ø680(+0.08/0) 대단부 보어를 캡 분할면과 평행한 방향으로만 재서 680.050(합격)으로 기록했다. 분할면에 직각 방향은 680.095로 상한을 넘었다 (볼트 체결로 보어가 세로로 늘어남). 원인: 측정 방향 부족. 주의사항: 대단부 보어는 분할면 평행·직각 2방향 × 입구·중간·안쪽 3단면(6점)을 재고, 가장 큰 값과 작은 값을 모두 기록한다. 조치: 6점 재측정 후 재호닝 여부 결정. 영향: 베어링 메탈 끼움 불량, 유막 불균일. 발생 단계: 정삭 후. 적용 조건: 캡 체결 상태 대단부 보어 정삭 후. 제외·확인 조건: 없음. 측정기 후보: 실린더 게이지, Ø680 세팅 링. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="120" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>소단부</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Ø560(+0.07/0)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 소단부 Ø560 H7을 크로스헤드 핀 Ø560 f7 공차와 혼동</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>소단부 보어 Ø560(+0.07/0)을 재면서 같은 화면에서 본 크로스헤드 핀 공차(-0.076/-0.146)로 판정 범위를 잡아 559.900을 합격 처리했다. 보어 하한은 560.000이다.</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>짝 부품 공차 혼동</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>구멍(H7)과 축(f7)은 같은 기준치수라도 공차 방향이 반대다. 측정 대상 부품·도면 번호와 화면의 허용 범위를 확인한다.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, Ø560 세팅 링</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>짝 부품과 같은 기준치수를 쓰는 끼워맞춤</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>소단부</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>크로스헤드 핀 조립 불가</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>보어 공차로 재판정</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 소단부, 내경, DIMENSION, Ø560(+0.07/0), 짝 부품 공차 혼동, 소단부, C3 도면 해석, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-035] 부품: 커넥팅로드. 부위: 소단부. 형상: 소단부(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø560(+0.07/0). 오류 유형: C3 도면 해석. 중요도: 상. 오류: [정삭] 소단부 Ø560 H7을 크로스헤드 핀 Ø560 f7 공차와 혼동. 상황: 소단부 보어 Ø560(+0.07/0)을 재면서 같은 화면에서 본 크로스헤드 핀 공차(-0.076/-0.146)로 판정 범위를 잡아 559.900을 합격 처리했다. 보어 하한은 560.000이다. 원인: 짝 부품 공차 혼동. 주의사항: 구멍(H7)과 축(f7)은 같은 기준치수라도 공차 방향이 반대다. 측정 대상 부품·도면 번호와 화면의 허용 범위를 확인한다. 조치: 보어 공차로 재판정. 영향: 크로스헤드 핀 조립 불가. 발생 단계: 정삭 후. 적용 조건: 짝 부품과 같은 기준치수를 쓰는 끼워맞춤. 제외·확인 조건: 없음. 측정기 후보: 실린더 게이지, Ø560 세팅 링. 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="120" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.8)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 호닝 보어 조도를 원주 방향으로 재서 크로스해치 영향이 빠짐</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>호닝한 대단부 보어(R1 = Ra 0.8)를 원주 방향으로 재서 Ra 0.35로 기록했다. 호닝 자국(크로스해치)은 축에 비스듬하므로 축 방향으로 재야 하며, 다시 재니 Ra 0.7이었다.</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>호닝면 측정 방향 오류</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>호닝 보어는 축 방향으로 촉침을 움직여 잰다. 입구·중간·안쪽 3곳을 재서 기록한다.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계(내경용 촉침)</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>호닝 보어 조도 측정</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>측정 방법</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>조도 과소 판정</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>축 방향으로 재측정</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 대단부, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.8), 호닝면 측정 방향 오류, 대단부, C5 측정 방법, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-036] 부품: 커넥팅로드. 부위: 대단부. 형상: 대단부(HOLE). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.8). 오류 유형: C5 측정 방법. 중요도: 중. 오류: [정삭] 호닝 보어 조도를 원주 방향으로 재서 크로스해치 영향이 빠짐. 상황: 호닝한 대단부 보어(R1 = Ra 0.8)를 원주 방향으로 재서 Ra 0.35로 기록했다. 호닝 자국(크로스해치)은 축에 비스듬하므로 축 방향으로 재야 하며, 다시 재니 Ra 0.7이었다. 원인: 호닝면 측정 방향 오류. 주의사항: 호닝 보어는 축 방향으로 촉침을 움직여 잰다. 입구·중간·안쪽 3곳을 재서 기록한다. 조치: 축 방향으로 재측정. 영향: 조도 과소 판정. 발생 단계: 정삭 후. 적용 조건: 호닝 보어 조도 측정. 제외·확인 조건: 없음. 측정기 후보: 표면조도계(내경용 촉침). 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Ø680(+0.08/0)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>공정</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>[중삭] 중삭 보링 떨림 자국을 호닝 여유로 지울 수 있다고 보고 넘김</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>캡 체결 후 대단부 중삭 보링에서 떨림 자국이 생겼는데 치수가 목표 범위라 그대로 호닝으로 넘겼다. 호닝 여유가 작아 자국이 남았고 R1(Ra 0.8)을 만족하지 못했다.</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>중삭 표면 상태 확인 누락</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>중삭 후 치수와 함께 보어 안쪽 떨림 자국을 확인한다. 자국 깊이가 호닝 여유보다 크면 보링 조건을 바꿔 다시 중삭한다.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, 육안 확인(조명)</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>호닝으로 마무리하는 보어 중삭 후</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>공정 추세·시삭</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>중삭 후</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>정삭 후 조도 불합격, 보어 확대</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>보링 조건 변경 후 재중삭</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 대단부, 내경, DIMENSION, Ø680(+0.08/0), 중삭 표면 상태 확인 누락, 대단부, C12 공정 추세·시삭, 중삭 후</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-037] 부품: 커넥팅로드. 부위: 대단부. 형상: 대단부(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø680(+0.08/0). 오류 유형: C12 공정 추세·시삭. 중요도: 상. 오류: [중삭] 중삭 보링 떨림 자국을 호닝 여유로 지울 수 있다고 보고 넘김. 상황: 캡 체결 후 대단부 중삭 보링에서 떨림 자국이 생겼는데 치수가 목표 범위라 그대로 호닝으로 넘겼다. 호닝 여유가 작아 자국이 남았고 R1(Ra 0.8)을 만족하지 못했다. 원인: 중삭 표면 상태 확인 누락. 주의사항: 중삭 후 치수와 함께 보어 안쪽 떨림 자국을 확인한다. 자국 깊이가 호닝 여유보다 크면 보링 조건을 바꿔 다시 중삭한다. 조치: 보링 조건 변경 후 재중삭. 영향: 정삭 후 조도 불합격, 보어 확대. 발생 단계: 중삭 후. 적용 조건: 호닝으로 마무리하는 보어 중삭 후. 제외·확인 조건: 없음. 측정기 후보: 실린더 게이지, 육안 확인(조명). 우선순위: 5(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="120" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>소단부</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Ø560(+0.07/0)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] 호닝 직후 소단부 보어를 재서 끼워맞춤 공차 일부가 온도로 사라짐</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>호닝 직후 보어 표면이 측정실보다 3℃ 높은 상태에서 Ø560을 재서 560.060(합격)으로 기록했다. 강은 Ø560에서 3℃당 약 0.019mm 커지므로, 식은 뒤 실제 값은 560.041 근처다. 반대로 하한 근처 값이면 식은 뒤 불합격이 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤면 온도 보정 누락</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 보어는 세팅 링과 부품 온도를 맞추고, 2℃ 이상 차이 나면 식힌 뒤 다시 잰다.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, 세팅 링, 표면 온도계</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>호닝·보링 직후 끼워맞춤 보어</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 측정한 경우 제외</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>소단부</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>온도·환경</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>성적서 값과 실제 치수 차이</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>온도 안정 후 재측정</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 소단부, 내경, DIMENSION, Ø560(+0.07/0), 끼워맞춤면 온도 보정 누락, 소단부, C9 온도·환경, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-038] 부품: 커넥팅로드. 부위: 소단부. 형상: 소단부(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø560(+0.07/0). 오류 유형: C9 온도·환경. 중요도: 중. 오류: [정삭] 호닝 직후 소단부 보어를 재서 끼워맞춤 공차 일부가 온도로 사라짐. 상황: 호닝 직후 보어 표면이 측정실보다 3℃ 높은 상태에서 Ø560을 재서 560.060(합격)으로 기록했다. 강은 Ø560에서 3℃당 약 0.019mm 커지므로, 식은 뒤 실제 값은 560.041 근처다. 반대로 하한 근처 값이면 식은 뒤 불합격이 될 수 있다. 원인: 끼워맞춤면 온도 보정 누락. 주의사항: 끼워맞춤 보어는 세팅 링과 부품 온도를 맞추고, 2℃ 이상 차이 나면 식힌 뒤 다시 잰다. 조치: 온도 안정 후 재측정. 영향: 성적서 값과 실제 치수 차이. 발생 단계: 정삭 후. 적용 조건: 호닝·보링 직후 끼워맞춤 보어. 제외·확인 조건: 온도 안정 후 측정한 경우 제외. 측정기 후보: 실린더 게이지, 세팅 링, 표면 온도계. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>표면 거칠기</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>SURFACE_ROUGHNESS</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>R1 (= Ra 0.8)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[공통] 조도 기호 R1을 반지름 1mm 모서리로 보고 측정 누락</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>대단부 보어 옆 'R1'을 모서리 반지름 1mm로 보고 확인만 했고 보어 조도는 재지 않았다. 표제란 범례상 R1·R2는 모두 Ra 0.8 조도 기호였다.</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>조도 기호와 반지름 치수 혼동</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>이 도면의 R1·R2는 표제란 범례의 조도 기호다. 관리자 검토 화면에서 조도로 분류됐는지 확인하고 표면조도계로 잰다.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>표면조도계</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>조도를 범례 기호(R1, R2)로 표기한 도면</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>실제 반지름 치수(R500)는 제외</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>대단부</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>도면 해석</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
+        <is>
+          <t>가공 공통</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>보어 조도 미측정</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>조도 측정 후 기록 추가</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>OCR은 R1을 Ri로 읽기도 하고, R1·R2를 반지름 치수로 분류한다</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 대단부, 표면 거칠기, SURFACE_ROUGHNESS, R1 (= Ra 0.8), 조도 기호와 반지름 치수 혼동, 대단부, C3 도면 해석, 가공 공통</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-039] 부품: 커넥팅로드. 부위: 대단부. 형상: 대단부(HOLE). 측정 특성: 표면 거칠기. 공차·검사 유형: SURFACE_ROUGHNESS. 도면 표기 예시: R1 (= Ra 0.8). 오류 유형: C3 도면 해석. 중요도: 중. 오류: [공통] 조도 기호 R1을 반지름 1mm 모서리로 보고 측정 누락. 상황: 대단부 보어 옆 'R1'을 모서리 반지름 1mm로 보고 확인만 했고 보어 조도는 재지 않았다. 표제란 범례상 R1·R2는 모두 Ra 0.8 조도 기호였다. 원인: 조도 기호와 반지름 치수 혼동. 주의사항: 이 도면의 R1·R2는 표제란 범례의 조도 기호다. 관리자 검토 화면에서 조도로 분류됐는지 확인하고 표면조도계로 잰다. 조치: 조도 측정 후 기록 추가. 영향: 보어 조도 미측정. 발생 단계: 가공 공통. 적용 조건: 조도를 범례 기호(R1, R2)로 표기한 도면. 제외·확인 조건: 실제 반지름 치수(R500)는 제외. 측정기 후보: 표면조도계. OCR 참고: OCR은 R1을 Ri로 읽기도 하고, R1·R2를 반지름 치수로 분류한다. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="120" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CR-M-040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SYNTHETIC</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>커넥팅로드</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>HOLE</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>소단부</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>내경</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>DIMENSION</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Ø560(+0.07/0)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>측정</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[정삭] Ø560 세팅 링 대신 Ø550 링으로 0점을 잡고 연장봉 차이를 계산</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Ø560 세팅 링이 없어 Ø550 링에 실린더 게이지 0점을 맞추고 연장봉 길이 차이 10mm를 더해 계산했다. 연장봉 길이 오차 0.01mm가 그대로 들어가 공차 폭 0.07mm의 15%가 셋팅 오차가 됐다.</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>기준 지름이 다른 세팅 링 사용</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>끼워맞춤 보어는 같은 기준치수의 세팅 링으로 0점을 잡는다. 없으면 내측 마이크로미터와 비교해 오차를 확인한 뒤 기록에 남긴다.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>실린더 게이지, Ø560 세팅 링</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>공차 폭 0.1mm 이하 보어</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>소단부</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>측정기</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>정삭 후</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>판정 오류</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>맞는 세팅 링으로 재측정</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>HOLE, 소단부, 내경, DIMENSION, Ø560(+0.07/0), 기준 지름이 다른 세팅 링 사용, 소단부, C4 측정기, 정삭 후</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>[가상 테스트 사례 CR-M-040] 부품: 커넥팅로드. 부위: 소단부. 형상: 소단부(HOLE). 측정 특성: 내경. 공차·검사 유형: DIMENSION. 도면 표기 예시: Ø560(+0.07/0). 오류 유형: C4 측정기. 중요도: 중. 오류: [정삭] Ø560 세팅 링 대신 Ø550 링으로 0점을 잡고 연장봉 차이를 계산. 상황: Ø560 세팅 링이 없어 Ø550 링에 실린더 게이지 0점을 맞추고 연장봉 길이 차이 10mm를 더해 계산했다. 연장봉 길이 오차 0.01mm가 그대로 들어가 공차 폭 0.07mm의 15%가 셋팅 오차가 됐다. 원인: 기준 지름이 다른 세팅 링 사용. 주의사항: 끼워맞춤 보어는 같은 기준치수의 세팅 링으로 0점을 잡는다. 없으면 내측 마이크로미터와 비교해 오차를 확인한 뒤 기록에 남긴다. 조치: 맞는 세팅 링으로 재측정. 영향: 판정 오류. 발생 단계: 정삭 후. 적용 조건: 공차 폭 0.1mm 이하 보어. 제외·확인 조건: 없음. 측정기 후보: 실린더 게이지, Ø560 세팅 링. 우선순위: 4(테스트 설정값).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA34"/>
+  <autoFilter ref="A1:AA41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5048,7 +5983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5634,6 +6569,125 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CR-M-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[정삭] 대단부 보어를 캡 분할 방향으로만 재서 타원을 놓침</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CR-M-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[정삭] 소단부 Ø560 H7을 크로스헤드 핀 Ø560 f7 공차와 혼동</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CR-M-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[정삭] 호닝 보어 조도를 원주 방향으로 재서 크로스해치 영향이 빠짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CR-M-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[중삭] 중삭 보링 떨림 자국을 호닝 여유로 지울 수 있다고 보고 넘김</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CR-M-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[정삭] 호닝 직후 소단부 보어를 재서 끼워맞춤 공차 일부가 온도로 사라짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CR-M-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[공통] 조도 기호 R1을 반지름 1mm 모서리로 보고 측정 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CR-M-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>새로 작성(HDH_CR_01 가공 기준)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[정삭] Ø560 세팅 링 대신 Ø550 링으로 0점을 잡고 연장봉 차이를 계산</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
